--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D2" t="n">
-        <v>12024</v>
+        <v>17867</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -488,78 +488,78 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+          <t>仅买入未平仓 300股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2594</v>
+        <v>2156</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>通富微电</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>6031</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>8950</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 100股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2837</v>
+        <v>2594</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>比亚迪</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>100</v>
       </c>
-      <c r="D4" t="n">
-        <v>6624</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>8950</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>512760</v>
+        <v>2837</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>芯片ETF</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10000</v>
+        <v>200</v>
       </c>
       <c r="D5" t="n">
-        <v>10970</v>
+        <v>13252</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -569,24 +569,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>仅买入未平仓 10000股（跨期持有底仓）</t>
+          <t>仅买入未平仓 200股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>561980</v>
+        <v>512760</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>芯片设备</t>
+          <t>芯片ETF</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="D6" t="n">
-        <v>4098</v>
+        <v>10970</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -596,24 +596,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仅买入未平仓 6000股（跨期持有底仓）</t>
+          <t>仅买入未平仓 10000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>600498</v>
+        <v>561980</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>芯片设备</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100</v>
+        <v>6000</v>
       </c>
       <c r="D7" t="n">
-        <v>4087</v>
+        <v>4098</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -623,24 +623,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>仅买入未平仓 6000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>601208</v>
+        <v>600498</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>4834</v>
+        <v>4087</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -656,18 +656,18 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>688008</v>
+        <v>601208</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>40094</v>
+        <v>9676</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -683,26 +683,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>688008</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>400</v>
+      </c>
+      <c r="D10" t="n">
+        <v>78934.12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 400股（跨期持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>688041</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>海光信息</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C11" t="n">
         <v>200</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>50368</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>仅买入未平仓 200股（跨期持有底仓）</t>
         </is>

--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="D2" t="n">
-        <v>17867</v>
+        <v>23590</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 300股（跨期持有底仓）</t>
+          <t>仅买入未平仓 400股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="D6" t="n">
-        <v>10970</v>
+        <v>14168</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -596,7 +596,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仅买入未平仓 10000股（跨期持有底仓）</t>
+          <t>仅买入未平仓 13000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="D7" t="n">
-        <v>4098</v>
+        <v>6746</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -623,7 +623,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅买入未平仓 6000股（跨期持有底仓）</t>
+          <t>仅买入未平仓 10000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="D10" t="n">
-        <v>78934.12</v>
+        <v>116938.12</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仅买入未平仓 400股（跨期持有底仓）</t>
+          <t>仅买入未平仓 600股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -732,6 +732,33 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>仅买入未平仓 200股（跨期持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>688778</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>厦钨新能</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>500</v>
+      </c>
+      <c r="F12" t="n">
+        <v>23195</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D2" t="n">
-        <v>23590</v>
+        <v>29213</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 400股（跨期持有底仓）</t>
+          <t>仅买入未平仓 500股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -521,45 +521,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2594</v>
+        <v>2222</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>6462</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>8950</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 100股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2837</v>
+        <v>2436</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>兴森科技</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>200</v>
       </c>
       <c r="D5" t="n">
-        <v>13252</v>
+        <v>6853</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -575,45 +575,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>512760</v>
+        <v>2594</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>芯片ETF</t>
+          <t>比亚迪</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>14168</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>8950</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仅买入未平仓 13000股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>561980</v>
+        <v>2837</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>芯片设备</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10000</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>6746</v>
+        <v>26107</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -623,24 +623,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅买入未平仓 10000股（跨期持有底仓）</t>
+          <t>仅买入未平仓 400股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>600498</v>
+        <v>512760</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>芯片ETF</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>13000</v>
       </c>
       <c r="D8" t="n">
-        <v>4087</v>
+        <v>14168</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -650,24 +650,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>仅买入未平仓 13000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>601208</v>
+        <v>561980</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>芯片设备</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>10000</v>
       </c>
       <c r="D9" t="n">
-        <v>9676</v>
+        <v>6746</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -677,24 +677,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+          <t>仅买入未平仓 10000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>688008</v>
+        <v>600498</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>116938.12</v>
+        <v>4087</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -704,24 +704,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仅买入未平仓 600股（跨期持有底仓）</t>
+          <t>仅买入未平仓 100股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>688041</v>
+        <v>601208</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>50368</v>
+        <v>9676</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -737,26 +737,80 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>688008</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>600</v>
+      </c>
+      <c r="D12" t="n">
+        <v>116938.12</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 600股（跨期持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>688041</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>200</v>
+      </c>
+      <c r="D13" t="n">
+        <v>50368</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>688778</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>厦钨新能</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
         <v>500</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F14" t="n">
         <v>23195</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,45 +521,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2222</v>
+        <v>2594</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>比亚迪</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>100</v>
       </c>
-      <c r="D4" t="n">
-        <v>6462</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>8950</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2436</v>
+        <v>2837</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>兴森科技</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>6853</v>
+        <v>26107</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -569,51 +569,51 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+          <t>仅买入未平仓 400股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2594</v>
+        <v>512760</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>芯片ETF</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>14168</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>8950</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 13000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2837</v>
+        <v>561980</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>芯片设备</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>10000</v>
       </c>
       <c r="D7" t="n">
-        <v>26107</v>
+        <v>6746</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -623,24 +623,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅买入未平仓 400股（跨期持有底仓）</t>
+          <t>仅买入未平仓 10000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>512760</v>
+        <v>600498</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>芯片ETF</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13000</v>
+        <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>14168</v>
+        <v>4087</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -650,24 +650,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仅买入未平仓 13000股（跨期持有底仓）</t>
+          <t>仅买入未平仓 100股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>561980</v>
+        <v>601208</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>芯片设备</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>6746</v>
+        <v>4838</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -677,24 +677,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>仅买入未平仓 10000股（跨期持有底仓）</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>600498</v>
+        <v>688041</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D10" t="n">
-        <v>4087</v>
+        <v>50368</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -704,113 +704,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>仅买入未平仓 200股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>601208</v>
+        <v>688778</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>厦钨新能</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>9676</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>23195</v>
       </c>
       <c r="G11" t="inlineStr">
-        <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>688008</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>澜起科技</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>600</v>
-      </c>
-      <c r="D12" t="n">
-        <v>116938.12</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>仅买入未平仓 600股（跨期持有底仓）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>688041</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>海光信息</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>200</v>
-      </c>
-      <c r="D13" t="n">
-        <v>50368</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>688778</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>厦钨新能</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>500</v>
-      </c>
-      <c r="F14" t="n">
-        <v>23195</v>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="D2" t="n">
-        <v>29213</v>
+        <v>34739</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 500股（跨期持有底仓）</t>
+          <t>仅买入未平仓 600股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -521,99 +521,99 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2594</v>
+        <v>2222</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>6578.5</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>8950</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2837</v>
+        <v>2436</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>兴森科技</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>26107</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3696.67</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>仅买入未平仓 400股（跨期持有底仓）</t>
+          <t>；仍卖出未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>512760</v>
+        <v>2594</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>芯片ETF</t>
+          <t>比亚迪</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>14168</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>8950</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仅买入未平仓 13000股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>561980</v>
+        <v>2837</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>芯片设备</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10000</v>
+        <v>600</v>
       </c>
       <c r="D7" t="n">
-        <v>6746</v>
+        <v>38778</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -623,24 +623,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅买入未平仓 10000股（跨期持有底仓）</t>
+          <t>仅买入未平仓 600股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>600498</v>
+        <v>300054</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>鼎龙股份</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D8" t="n">
-        <v>4087</v>
+        <v>13546</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -650,24 +650,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>仅买入未平仓 200股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>601208</v>
+        <v>512760</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>芯片ETF</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>100</v>
+        <v>13000</v>
       </c>
       <c r="D9" t="n">
-        <v>4838</v>
+        <v>14168</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -677,24 +677,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仅买入未平仓 13000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>688041</v>
+        <v>561980</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>芯片设备</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>200</v>
+        <v>20000</v>
       </c>
       <c r="D10" t="n">
-        <v>50368</v>
+        <v>13316</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -704,32 +704,140 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+          <t>仅买入未平仓 20000股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>600498</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>烽火通信</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4087</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>601208</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>200</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9651.33</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>仍买入未平仓 200股</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>688008</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>200</v>
+      </c>
+      <c r="D13" t="n">
+        <v>39060.43</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>仍买入未平仓 200股</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>688041</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>200</v>
+      </c>
+      <c r="D14" t="n">
+        <v>50368</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>688778</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>厦钨新能</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
         <v>500</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F15" t="n">
         <v>23195</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D11" t="n">
-        <v>4087</v>
+        <v>12287</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -731,7 +731,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>仅买入未平仓 300股（跨期持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026-09.xlsx
+++ b/reports/剩余持仓_2026-09.xlsx
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D8" t="n">
-        <v>13546</v>
+        <v>27020</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨期持有底仓）</t>
+          <t>仅买入未平仓 400股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>9651.33</v>
+        <v>4825.67</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>仍买入未平仓 200股</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
